--- a/Haptics Symposium Version 2026/Hardware/Parts to Order BOM.xlsx
+++ b/Haptics Symposium Version 2026/Hardware/Parts to Order BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdm0115\Documents\GitHub\hAUptic-paddle\Haptic Symposium Version 2026\Hardware\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdm0115\Documents\GitHub\hAUptic-paddle\Haptics Symposium Version 2026\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3556F257-3484-43DB-9B3F-23CE3062631A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B14D47-B65B-479F-A9A0-27030F096BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4EECC354-6FBD-4068-A1E6-CB27AE90A32C}"/>
+    <workbookView xWindow="7305" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{4EECC354-6FBD-4068-A1E6-CB27AE90A32C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="67">
   <si>
     <t>Item</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Price Per Paddle</t>
   </si>
   <si>
-    <t>Contact ____________________</t>
-  </si>
-  <si>
     <t>If Desired/Needed for Connection</t>
   </si>
   <si>
@@ -213,6 +210,33 @@
   </si>
   <si>
     <t>Necessary if lacking a USB/USB-C Cable</t>
+  </si>
+  <si>
+    <t>Digikey</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/seeed-technology-co-ltd/113991114/19285530?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20243136172&amp;gbraid=0AAAAADrbLljzjhqW8GEuzyu6roKO8B0hL&amp;gclid=CjwKCAiAncvMBhBEEiwA9GU_fjDVjtTE7Fk0g16dPo1ecD7XRxhsBB5pOPxcmgkVP8jmFqzQbLufMhoC1ugQAvD_BwE</t>
+  </si>
+  <si>
+    <t>Xiao Seeed ESP32S3</t>
+  </si>
+  <si>
+    <t>Without WiFI</t>
+  </si>
+  <si>
+    <t>With WiFi</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>**Version Used for Work-in-Progress Interface and Design Upgrades to Design Paper (Haptics Symposium 2026)</t>
+  </si>
+  <si>
+    <t>**Version Used for Evaluating Usability Between Low Cost and High End Haptic Paddles (Haptics Symposium 2026)</t>
+  </si>
+  <si>
+    <t>Contact ___mdm0115@auburn.edu____</t>
   </si>
 </sst>
 </file>
@@ -368,7 +392,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -414,6 +438,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -475,14 +502,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90B5E59A-A125-497C-9ED9-FE2CB617AC56}" name="Table2" displayName="Table2" ref="A1:G19" totalsRowShown="0">
-  <autoFilter ref="A1:G19" xr:uid="{90B5E59A-A125-497C-9ED9-FE2CB617AC56}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{90B5E59A-A125-497C-9ED9-FE2CB617AC56}" name="Table2" displayName="Table2" ref="A1:H20" totalsRowShown="0">
+  <autoFilter ref="A1:H20" xr:uid="{90B5E59A-A125-497C-9ED9-FE2CB617AC56}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{937D295C-DE30-46A1-BDC1-6C39079923D6}" name="Item" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{526B8FD6-BCED-4741-8565-D009D113F262}" name="Cost Per Pack"/>
     <tableColumn id="3" xr3:uid="{17F63AA0-6CCF-4E57-B71D-A5AE82DCB6F9}" name="No. Per Pack"/>
@@ -490,6 +513,7 @@
     <tableColumn id="5" xr3:uid="{B38DA5F5-2B19-4A9E-81FB-F343D7DA8F77}" name="Cost Per Paddle"/>
     <tableColumn id="6" xr3:uid="{A36C93C6-D9F1-4C1E-9ADD-530F23F77151}" name="Vendor"/>
     <tableColumn id="7" xr3:uid="{AA3A03BA-D911-45D3-988F-706BDD60123A}" name="Link"/>
+    <tableColumn id="8" xr3:uid="{6B05F40C-B9B9-4C42-B479-6E5F2CFE1042}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -812,7 +836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA44F03A-B9F7-496D-A400-0D3F72C46D68}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" customWidth="1"/>
@@ -824,7 +848,7 @@
     <col min="7" max="7" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -846,8 +870,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
@@ -861,7 +888,7 @@
         <v>0.2</v>
       </c>
       <c r="E2" s="9">
-        <f t="shared" ref="E2:E18" si="0">B2*(D2/C2)</f>
+        <f t="shared" ref="E2:E19" si="0">B2*(D2/C2)</f>
         <v>5.6000000000000005</v>
       </c>
       <c r="F2" s="7" t="s">
@@ -871,482 +898,497 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="6">
+        <v>7.49</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9">
+        <f t="shared" si="0"/>
+        <v>7.49</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B4" s="24">
         <v>6.5</v>
       </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="25">
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="25">
         <f t="shared" si="0"/>
         <v>6.5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G4" s="5" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="H4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B5" s="22">
         <v>12.95</v>
       </c>
-      <c r="C4" s="23">
-        <v>1</v>
-      </c>
-      <c r="D4" s="23">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="C5" s="23">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
         <f t="shared" si="0"/>
         <v>12.95</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F5" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G5" s="27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B6" s="24">
         <v>14.5</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="25">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="25">
         <f t="shared" si="0"/>
         <v>14.5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B7" s="6">
         <v>15</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C7" s="7">
         <v>33</v>
       </c>
-      <c r="D6" s="8">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9">
         <f t="shared" si="0"/>
         <v>0.45454545454545459</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G7" s="10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B8" s="24">
         <v>4.95</v>
       </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="25">
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25">
         <f t="shared" si="0"/>
         <v>4.95</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="26" t="s">
+      <c r="G8" s="26" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B9" s="6">
         <v>0.92</v>
       </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="C9" s="7">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
         <f t="shared" si="0"/>
         <v>0.92</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F9" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G9" s="15" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="1">
         <v>6.88</v>
       </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="C10" s="2">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
         <f t="shared" si="0"/>
         <v>6.88</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G10" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B11" s="6">
         <v>1.27</v>
       </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
         <f>(1/12)</f>
         <v>8.3333333333333329E-2</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E11" s="9">
         <f t="shared" si="0"/>
         <v>0.10583333333333333</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G11" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B12" s="1">
         <v>7.39</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C12" s="2">
         <v>50</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D12" s="3">
         <v>5</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>0.73899999999999999</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G12" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B13" s="6">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C13" s="7">
         <v>32.81</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D13" s="8">
         <v>0.5</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E13" s="9">
         <f t="shared" si="0"/>
         <v>0.13715330691862235</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="G12" s="10" t="s">
+      <c r="G13" s="10" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
+    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B14" s="1">
         <v>3.93</v>
       </c>
-      <c r="C13" s="2">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
         <f t="shared" si="0"/>
         <v>3.93</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B15" s="6">
         <v>1.91</v>
       </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="C15" s="7">
+        <v>1</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="9">
         <f t="shared" si="0"/>
         <v>1.91</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G15" s="10" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B16" s="1">
         <v>9.99</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C16" s="2">
         <v>60</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D16" s="3">
         <f>1/8</f>
         <v>0.125</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E16" s="4">
         <f t="shared" si="0"/>
         <v>2.0812500000000001E-2</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G16" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B17" s="6">
         <v>2.33</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C17" s="7">
         <v>100</v>
       </c>
-      <c r="D16" s="8">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9">
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9">
         <f t="shared" si="0"/>
         <v>2.3300000000000001E-2</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G17" s="10" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
+    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B18" s="1">
         <v>2.02</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C18" s="2">
         <v>100</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D18" s="3">
         <v>4</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E18" s="4">
         <f t="shared" si="0"/>
         <v>8.0799999999999997E-2</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G18" s="5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="29">
+      <c r="B19" s="29">
         <v>2.33</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C19" s="23">
         <v>100</v>
       </c>
-      <c r="D18" s="23">
-        <v>1</v>
-      </c>
-      <c r="E18" s="30">
+      <c r="D19" s="23">
+        <v>1</v>
+      </c>
+      <c r="E19" s="30">
         <f t="shared" si="0"/>
         <v>2.3300000000000001E-2</v>
       </c>
-      <c r="F18" s="23" t="s">
+      <c r="F19" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="27" t="s">
+      <c r="G19" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="H18" s="23"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B20" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="21">
+        <v>2.33</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="17">
+        <f xml:space="preserve"> SUM(E2:E20)-E3</f>
+        <v>62.05474459479742</v>
+      </c>
+      <c r="F22" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E23" s="17">
+        <f xml:space="preserve"> SUM(E1:E20)-E4</f>
+        <v>63.044744594797422</v>
+      </c>
+      <c r="F23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="21">
-        <v>2.33</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="17">
-        <f xml:space="preserve"> SUM(E2:E19)</f>
-        <v>62.054744594797405</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    </row>
+    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="31" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
+      <c r="B26" s="28">
+        <v>24.94</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26" s="13">
+        <v>4</v>
+      </c>
+      <c r="E26" s="28">
+        <f>B26*(D26/C26)</f>
+        <v>9.9760000000000009</v>
+      </c>
+      <c r="F26" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I26" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="28">
-        <v>24.94</v>
-      </c>
-      <c r="C25">
-        <v>10</v>
-      </c>
-      <c r="D25" s="13">
-        <v>4</v>
-      </c>
-      <c r="E25" s="28">
-        <f>B25*(D25/C25)</f>
-        <v>9.9760000000000009</v>
-      </c>
-      <c r="F25" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+    </row>
+    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="12">
+      <c r="B27" s="12">
         <v>13.99</v>
-      </c>
-      <c r="C26" s="13">
-        <v>2</v>
-      </c>
-      <c r="D26" s="14">
-        <v>1</v>
-      </c>
-      <c r="E26" s="32">
-        <f>B26*(D26/C26)</f>
-        <v>6.9950000000000001</v>
-      </c>
-      <c r="F26" t="s">
-        <v>7</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="12">
-        <v>13</v>
       </c>
       <c r="C27" s="13">
         <v>2</v>
@@ -1356,39 +1398,66 @@
       </c>
       <c r="E27" s="32">
         <f>B27*(D27/C27)</f>
-        <v>6.5</v>
+        <v>6.9950000000000001</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
       </c>
       <c r="G27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="12">
+        <v>13</v>
+      </c>
+      <c r="C28" s="13">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="32">
+        <f>B28*(D28/C28)</f>
+        <v>6.5</v>
+      </c>
+      <c r="F28" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I27" t="s">
-        <v>58</v>
+      <c r="I28" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{70A46ECE-F389-4C1F-8EF6-D36F7A4EBB22}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{8F99B7C3-DA5C-4A7D-96EC-98A05D9E9865}"/>
-    <hyperlink ref="G6" r:id="rId3" xr:uid="{D2666D17-40B0-44FE-857B-E1D3C22B1EA3}"/>
-    <hyperlink ref="G26" r:id="rId4" display="https://www.amazon.com/ALITOVE-Converter-100-240V-Transformer-Security/dp/B082C6XF88/ref=sr_1_5_sspa?dib=eyJ2IjoiMSJ9.HhyQcYFxSnAV0hq4e0qwVBIIaRB1Q8r-ej1UXmJNTW8NzWFN2F8Kja5vI4VILzOGMPnTERPdwN2UdlZgl_8yWNeucQPLlVl7olA2PaO0OlbbiFRclV5RnabcmtfD7SAq-frUYzAmI241VV2ItsFQJEKEe75MX-bysCqoT0xBRFZKvZMtxHHv2PNpyXA8pQcAvMzf5SSSd_SnFhYdW2aGy9JMr3OMyje5iaucrT8DbBo.6soFbMssKnysD5ttN_XiPOlMUxVfTFENRqQ6dihE7_s&amp;dib_tag=se&amp;hvadid=694095447987&amp;hvdev=c&amp;hvexpln=67&amp;hvlocphy=1012947&amp;hvnetw=g&amp;hvocijid=7647249868743066757--&amp;hvqmt=e&amp;hvrand=7647249868743066757&amp;hvtargid=kwd-1028416465885&amp;hydadcr=12727_13368272&amp;keywords=ac%2Badapter%2Bmodel%2Brxz12v2a-a&amp;mcid=9366ef7bda583eeb848b7585e2c55389&amp;qid=1759790868&amp;sr=8-5-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;th=1" xr:uid="{576C729D-6B75-4BF6-B3F2-90EA06D69BB6}"/>
-    <hyperlink ref="G27" r:id="rId5" xr:uid="{1CC738D3-54B0-49DD-AA95-1AE8395007A3}"/>
-    <hyperlink ref="G9" r:id="rId6" xr:uid="{B2333FEF-C4B7-48DD-9D6B-40EEC6F0A8A6}"/>
-    <hyperlink ref="G8" r:id="rId7" xr:uid="{2BD44896-4B6C-4FFF-9F66-08D06CC30850}"/>
-    <hyperlink ref="G25" r:id="rId8" xr:uid="{984B5CF7-8842-4F51-B99F-97F749EB3314}"/>
-    <hyperlink ref="G10" r:id="rId9" xr:uid="{23735F81-3EBF-4FAB-8AAB-8BB176F1DA3A}"/>
-    <hyperlink ref="G15" r:id="rId10" xr:uid="{D878B01D-78E4-4D58-8A1E-C3DB4D704ABA}"/>
-    <hyperlink ref="G13" r:id="rId11" xr:uid="{930111AC-04C1-4B12-B8AB-9096730E9195}"/>
-    <hyperlink ref="G11" r:id="rId12" xr:uid="{99949F7E-F2CC-4333-AA2D-F3BD463EF288}"/>
-    <hyperlink ref="G12" r:id="rId13" xr:uid="{549CE53F-B0C7-4C5B-B85A-D7AF03CBD222}"/>
-    <hyperlink ref="G14" r:id="rId14" xr:uid="{AAA5BC7C-E4C9-45B7-A8A8-A52BAE95A982}"/>
-    <hyperlink ref="G16" r:id="rId15" xr:uid="{194B7E17-DDB6-4552-93D1-D0187097E6A9}"/>
-    <hyperlink ref="G17" r:id="rId16" xr:uid="{A1E4A2AC-86DD-45B7-BFCF-DD6CC9814CBE}"/>
-    <hyperlink ref="G7" r:id="rId17" xr:uid="{6ED6AB8D-1AAB-455D-BC86-7BE2AB006635}"/>
-    <hyperlink ref="G5" r:id="rId18" xr:uid="{42CC261C-6017-49B7-898F-C0226203C362}"/>
-    <hyperlink ref="G4" r:id="rId19" xr:uid="{D3DDA209-B417-4B6F-A7B4-8C9B75D8FDEF}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{D2666D17-40B0-44FE-857B-E1D3C22B1EA3}"/>
+    <hyperlink ref="G27" r:id="rId3" display="https://www.amazon.com/ALITOVE-Converter-100-240V-Transformer-Security/dp/B082C6XF88/ref=sr_1_5_sspa?dib=eyJ2IjoiMSJ9.HhyQcYFxSnAV0hq4e0qwVBIIaRB1Q8r-ej1UXmJNTW8NzWFN2F8Kja5vI4VILzOGMPnTERPdwN2UdlZgl_8yWNeucQPLlVl7olA2PaO0OlbbiFRclV5RnabcmtfD7SAq-frUYzAmI241VV2ItsFQJEKEe75MX-bysCqoT0xBRFZKvZMtxHHv2PNpyXA8pQcAvMzf5SSSd_SnFhYdW2aGy9JMr3OMyje5iaucrT8DbBo.6soFbMssKnysD5ttN_XiPOlMUxVfTFENRqQ6dihE7_s&amp;dib_tag=se&amp;hvadid=694095447987&amp;hvdev=c&amp;hvexpln=67&amp;hvlocphy=1012947&amp;hvnetw=g&amp;hvocijid=7647249868743066757--&amp;hvqmt=e&amp;hvrand=7647249868743066757&amp;hvtargid=kwd-1028416465885&amp;hydadcr=12727_13368272&amp;keywords=ac%2Badapter%2Bmodel%2Brxz12v2a-a&amp;mcid=9366ef7bda583eeb848b7585e2c55389&amp;qid=1759790868&amp;sr=8-5-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9tdGY&amp;th=1" xr:uid="{576C729D-6B75-4BF6-B3F2-90EA06D69BB6}"/>
+    <hyperlink ref="G28" r:id="rId4" xr:uid="{1CC738D3-54B0-49DD-AA95-1AE8395007A3}"/>
+    <hyperlink ref="G10" r:id="rId5" xr:uid="{B2333FEF-C4B7-48DD-9D6B-40EEC6F0A8A6}"/>
+    <hyperlink ref="G9" r:id="rId6" xr:uid="{2BD44896-4B6C-4FFF-9F66-08D06CC30850}"/>
+    <hyperlink ref="G26" r:id="rId7" xr:uid="{984B5CF7-8842-4F51-B99F-97F749EB3314}"/>
+    <hyperlink ref="G11" r:id="rId8" xr:uid="{23735F81-3EBF-4FAB-8AAB-8BB176F1DA3A}"/>
+    <hyperlink ref="G16" r:id="rId9" xr:uid="{D878B01D-78E4-4D58-8A1E-C3DB4D704ABA}"/>
+    <hyperlink ref="G14" r:id="rId10" xr:uid="{930111AC-04C1-4B12-B8AB-9096730E9195}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{99949F7E-F2CC-4333-AA2D-F3BD463EF288}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{549CE53F-B0C7-4C5B-B85A-D7AF03CBD222}"/>
+    <hyperlink ref="G15" r:id="rId13" xr:uid="{AAA5BC7C-E4C9-45B7-A8A8-A52BAE95A982}"/>
+    <hyperlink ref="G17" r:id="rId14" xr:uid="{194B7E17-DDB6-4552-93D1-D0187097E6A9}"/>
+    <hyperlink ref="G18" r:id="rId15" xr:uid="{A1E4A2AC-86DD-45B7-BFCF-DD6CC9814CBE}"/>
+    <hyperlink ref="G8" r:id="rId16" xr:uid="{6ED6AB8D-1AAB-455D-BC86-7BE2AB006635}"/>
+    <hyperlink ref="G6" r:id="rId17" xr:uid="{42CC261C-6017-49B7-898F-C0226203C362}"/>
+    <hyperlink ref="G5" r:id="rId18" xr:uid="{D3DDA209-B417-4B6F-A7B4-8C9B75D8FDEF}"/>
+    <hyperlink ref="G4" r:id="rId19" xr:uid="{8F99B7C3-DA5C-4A7D-96EC-98A05D9E9865}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1398,23 +1467,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bb1258de-dfc0-4e5e-a08f-915a2a257543" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100AD326CB7A09A0F4C8FB5EF08E11BB1CA" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b96899a4064ebb50806c63fedfe1305a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="bb1258de-dfc0-4e5e-a08f-915a2a257543" xmlns:ns4="a328147a-d6f3-4bcf-b334-baa5cad3d9e3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91be5b736da33c8cb1bfd4fdbb176150" ns3:_="" ns4:_="">
     <xsd:import namespace="bb1258de-dfc0-4e5e-a08f-915a2a257543"/>
@@ -1673,32 +1725,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781CF981-5968-4F0C-99C2-5D75F84EAFBD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bb1258de-dfc0-4e5e-a08f-915a2a257543"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="a328147a-d6f3-4bcf-b334-baa5cad3d9e3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42517E9-003E-4DE9-88C1-DCADA1A3F064}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bb1258de-dfc0-4e5e-a08f-915a2a257543" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501621A6-8E83-4559-BD22-3B2CE4FCDE25}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1715,4 +1759,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42517E9-003E-4DE9-88C1-DCADA1A3F064}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781CF981-5968-4F0C-99C2-5D75F84EAFBD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bb1258de-dfc0-4e5e-a08f-915a2a257543"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a328147a-d6f3-4bcf-b334-baa5cad3d9e3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Haptics Symposium Version 2026/Hardware/Parts to Order BOM.xlsx
+++ b/Haptics Symposium Version 2026/Hardware/Parts to Order BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdm0115\Documents\GitHub\hAUptic-paddle\Haptics Symposium Version 2026\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34B14D47-B65B-479F-A9A0-27030F096BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5AEF5AB-E1D4-4B79-8A98-8F1855933DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7305" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{4EECC354-6FBD-4068-A1E6-CB27AE90A32C}"/>
+    <workbookView xWindow="3405" yWindow="1260" windowWidth="21600" windowHeight="11295" xr2:uid="{4EECC354-6FBD-4068-A1E6-CB27AE90A32C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,15 +77,9 @@
     <t>https://www.mouser.com/ProductDetail/Seeed-Studio/102010388?qs=hd1VzrDQEGhCsl7tLa3o%252Bg%3D%3D&amp;mgh=1</t>
   </si>
   <si>
-    <t>Voltage Regulator (Pololu 0J8557)</t>
-  </si>
-  <si>
     <t>Pololu</t>
   </si>
   <si>
-    <t>https://www.pololu.com/product/2834/specs</t>
-  </si>
-  <si>
     <t>Motor Drivers</t>
   </si>
   <si>
@@ -173,9 +167,6 @@
     <t>Sensor</t>
   </si>
   <si>
-    <t>https://www.mouser.com/ProductDetail/Allegro-MicroSystems/A1369EUA-24-T?qs=pUKx8fyJudATg4m7%252BSXxxQ%3D%3D</t>
-  </si>
-  <si>
     <t>Female header connector</t>
   </si>
   <si>
@@ -237,6 +228,15 @@
   </si>
   <si>
     <t>Contact ___mdm0115@auburn.edu____</t>
+  </si>
+  <si>
+    <t>5V Voltage Regulator (Pololu 0J8557)</t>
+  </si>
+  <si>
+    <t>Pololu 5V, 500mA Step-Down Voltage Regulator D24V5F5</t>
+  </si>
+  <si>
+    <t>SS49E Honeywell Sensing and Productivity Solutions | Linear, Compass (ICs) | DigiKey</t>
   </si>
 </sst>
 </file>
@@ -392,7 +392,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -438,9 +438,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -871,7 +868,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -899,8 +896,8 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="33" t="s">
-        <v>60</v>
+      <c r="A3" s="20" t="s">
+        <v>57</v>
       </c>
       <c r="B3" s="6">
         <v>7.49</v>
@@ -916,13 +913,13 @@
         <v>7.49</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="H3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -949,15 +946,15 @@
         <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="B5" s="22">
-        <v>12.95</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="C5" s="23">
         <v>1</v>
@@ -967,18 +964,18 @@
       </c>
       <c r="E5" s="9">
         <f t="shared" si="0"/>
-        <v>12.95</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="F5" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="27" t="s">
-        <v>15</v>
+        <v>13</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" s="24">
         <v>14.5</v>
@@ -994,15 +991,15 @@
         <v>14.5</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="6">
         <v>15</v>
@@ -1021,12 +1018,12 @@
         <v>7</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B8" s="24">
         <v>4.95</v>
@@ -1042,15 +1039,15 @@
         <v>4.95</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B9" s="6">
         <v>0.92</v>
@@ -1066,15 +1063,15 @@
         <v>0.92</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1">
         <v>6.88</v>
@@ -1090,15 +1087,15 @@
         <v>6.88</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B11" s="6">
         <v>1.27</v>
@@ -1115,15 +1112,15 @@
         <v>0.10583333333333333</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1">
         <v>7.39</v>
@@ -1142,12 +1139,12 @@
         <v>7</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6">
         <v>9</v>
@@ -1166,12 +1163,12 @@
         <v>7</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1">
         <v>3.93</v>
@@ -1187,18 +1184,18 @@
         <v>3.93</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="6">
-        <v>1.91</v>
+        <v>6.65</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -1208,18 +1205,18 @@
       </c>
       <c r="E15" s="9">
         <f t="shared" si="0"/>
-        <v>1.91</v>
+        <v>6.65</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B16" s="1">
         <v>9.99</v>
@@ -1239,12 +1236,12 @@
         <v>7</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="18" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B17" s="6">
         <v>2.33</v>
@@ -1260,15 +1257,15 @@
         <v>2.3300000000000001E-2</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="20" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1">
         <v>2.02</v>
@@ -1284,15 +1281,15 @@
         <v>8.0799999999999997E-2</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="20" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" s="29">
         <v>2.33</v>
@@ -1308,19 +1305,19 @@
         <v>2.3300000000000001E-2</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H19" s="23"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="20" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
@@ -1332,33 +1329,33 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="D22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E22" s="17">
         <f xml:space="preserve"> SUM(E2:E20)-E3</f>
-        <v>62.05474459479742</v>
+        <v>62.794744594797429</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E23" s="17">
         <f xml:space="preserve"> SUM(E1:E20)-E4</f>
-        <v>63.044744594797422</v>
+        <v>63.784744594797431</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B26" s="28">
         <v>24.94</v>
@@ -1374,18 +1371,18 @@
         <v>9.9760000000000009</v>
       </c>
       <c r="F26" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I26" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B27" s="12">
         <v>13.99</v>
@@ -1404,15 +1401,15 @@
         <v>7</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B28" s="12">
         <v>13</v>
@@ -1431,10 +1428,10 @@
         <v>7</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1451,13 +1448,13 @@
     <hyperlink ref="G14" r:id="rId10" xr:uid="{930111AC-04C1-4B12-B8AB-9096730E9195}"/>
     <hyperlink ref="G12" r:id="rId11" xr:uid="{99949F7E-F2CC-4333-AA2D-F3BD463EF288}"/>
     <hyperlink ref="G13" r:id="rId12" xr:uid="{549CE53F-B0C7-4C5B-B85A-D7AF03CBD222}"/>
-    <hyperlink ref="G15" r:id="rId13" xr:uid="{AAA5BC7C-E4C9-45B7-A8A8-A52BAE95A982}"/>
-    <hyperlink ref="G17" r:id="rId14" xr:uid="{194B7E17-DDB6-4552-93D1-D0187097E6A9}"/>
-    <hyperlink ref="G18" r:id="rId15" xr:uid="{A1E4A2AC-86DD-45B7-BFCF-DD6CC9814CBE}"/>
-    <hyperlink ref="G8" r:id="rId16" xr:uid="{6ED6AB8D-1AAB-455D-BC86-7BE2AB006635}"/>
-    <hyperlink ref="G6" r:id="rId17" xr:uid="{42CC261C-6017-49B7-898F-C0226203C362}"/>
-    <hyperlink ref="G5" r:id="rId18" xr:uid="{D3DDA209-B417-4B6F-A7B4-8C9B75D8FDEF}"/>
-    <hyperlink ref="G4" r:id="rId19" xr:uid="{8F99B7C3-DA5C-4A7D-96EC-98A05D9E9865}"/>
+    <hyperlink ref="G17" r:id="rId13" xr:uid="{194B7E17-DDB6-4552-93D1-D0187097E6A9}"/>
+    <hyperlink ref="G18" r:id="rId14" xr:uid="{A1E4A2AC-86DD-45B7-BFCF-DD6CC9814CBE}"/>
+    <hyperlink ref="G8" r:id="rId15" xr:uid="{6ED6AB8D-1AAB-455D-BC86-7BE2AB006635}"/>
+    <hyperlink ref="G6" r:id="rId16" xr:uid="{42CC261C-6017-49B7-898F-C0226203C362}"/>
+    <hyperlink ref="G4" r:id="rId17" xr:uid="{8F99B7C3-DA5C-4A7D-96EC-98A05D9E9865}"/>
+    <hyperlink ref="G5" r:id="rId18" display="https://www.pololu.com/product/2843" xr:uid="{408B4FC5-237B-4D3D-92DE-9A5D9A1D1460}"/>
+    <hyperlink ref="G15" r:id="rId19" display="https://www.digikey.com.au/en/products/detail/honeywell-sensing-and-productivity-solutions/SS49E/701361" xr:uid="{D077DA89-712D-4096-8803-F8C05A9198BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -1726,20 +1723,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="bb1258de-dfc0-4e5e-a08f-915a2a257543" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="bb1258de-dfc0-4e5e-a08f-915a2a257543" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1762,14 +1759,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42517E9-003E-4DE9-88C1-DCADA1A3F064}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{781CF981-5968-4F0C-99C2-5D75F84EAFBD}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -1784,4 +1773,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E42517E9-003E-4DE9-88C1-DCADA1A3F064}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>